--- a/api/1/xlsx/es/OrganisationRegistrationAgency.xlsx
+++ b/api/1/xlsx/es/OrganisationRegistrationAgency.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2169" uniqueCount="1336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2186" uniqueCount="1344">
   <si>
     <t>code</t>
   </si>
@@ -538,7 +538,7 @@
     <t>BR</t>
   </si>
   <si>
-    <t>http://cnpj.info/</t>
+    <t>https://www.gov.br/pt-br/servicos/consultar-cadastro-nacional-de-pessoas-juridicas</t>
   </si>
   <si>
     <t>BR-COA</t>
@@ -970,7 +970,7 @@
     <t>CZ-DIC</t>
   </si>
   <si>
-    <t>http://www.kurzy.cz/dic/</t>
+    <t>https://mfcr.cz/en/regulation-and-taxes/taxes</t>
   </si>
   <si>
     <t>CZ-ICO</t>
@@ -991,7 +991,7 @@
     <t>DE-CR</t>
   </si>
   <si>
-    <t>https://www.handelsregister.de/rp_web/welcome.do</t>
+    <t>https://www.handelsregister.de/rp_web/welcome.xhtml</t>
   </si>
   <si>
     <t>DJ-COA</t>
@@ -1162,7 +1162,7 @@
     <t>ET-CSA</t>
   </si>
   <si>
-    <t>http://www.chsa.gov.et/</t>
+    <t>https://acso.gov.et/</t>
   </si>
   <si>
     <t>ET-MFA</t>
@@ -2755,7 +2755,7 @@
     <t>NP-CRO</t>
   </si>
   <si>
-    <t>http://www.cro.gov.np/</t>
+    <t>https://www.ocr.gov.np/</t>
   </si>
   <si>
     <t>NP-IRD</t>
@@ -2860,6 +2860,12 @@
     <t>https://gov-id-finder.codeforiati.org/countries/PG/</t>
   </si>
   <si>
+    <t>PG-IPA</t>
+  </si>
+  <si>
+    <t>http://www.ipa.gov.pg/</t>
+  </si>
+  <si>
     <t>PH-COA</t>
   </si>
   <si>
@@ -3121,7 +3127,7 @@
     <t>RW-RRA</t>
   </si>
   <si>
-    <t>https://www.rra.gov.rw/index.php?id=45&amp;L=1%27A%3D0</t>
+    <t>https://www.rra.gov.rw/en/home</t>
   </si>
   <si>
     <t>SA-COA</t>
@@ -3133,12 +3139,18 @@
     <t>https://gov-id-finder.codeforiati.org/countries/SA/</t>
   </si>
   <si>
+    <t>SB-BR</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t>https://www.solomonbusinessregistry.gov.sb/</t>
+  </si>
+  <si>
     <t>SB-COA</t>
   </si>
   <si>
-    <t>SB</t>
-  </si>
-  <si>
     <t>https://gov-id-finder.codeforiati.org/countries/SB/</t>
   </si>
   <si>
@@ -3373,7 +3385,7 @@
     <t>SV-NIT</t>
   </si>
   <si>
-    <t>https://www.transparencia.gob.sv/institutions/dgii/services/7180</t>
+    <t>https://www.mh.gob.sv/</t>
   </si>
   <si>
     <t>SX-COA</t>
@@ -3547,6 +3559,12 @@
     <t>https://www.dernekler.gov.tr/</t>
   </si>
   <si>
+    <t>TR-VKN</t>
+  </si>
+  <si>
+    <t>https://www.gib.gov.tr/</t>
+  </si>
+  <si>
     <t>TT-COA</t>
   </si>
   <si>
@@ -3646,7 +3664,7 @@
     <t>UG-RSB</t>
   </si>
   <si>
-    <t>http://www.ursb.go.ug/</t>
+    <t>https://ursb.go.ug/</t>
   </si>
   <si>
     <t>UM-COA</t>
@@ -3775,6 +3793,12 @@
     <t>https://www.most.gov.vn/en/Pages/home.aspx</t>
   </si>
   <si>
+    <t>VN-TIN</t>
+  </si>
+  <si>
+    <t>https://vbpl.vn/TW/Pages/vbpqen-toanvan.aspx?ItemID=5946</t>
+  </si>
+  <si>
     <t>VU-COA</t>
   </si>
   <si>
@@ -3883,7 +3907,7 @@
     <t>XM-DAC</t>
   </si>
   <si>
-    <t>http://www.oecd.org/dac/stats/dacandcrscodelists.htm</t>
+    <t>https://development-finance-codelists.oecd.org/CodesList.aspx</t>
   </si>
   <si>
     <t>XM-OCHA</t>
@@ -3949,7 +3973,7 @@
     <t>ZA</t>
   </si>
   <si>
-    <t>http://www.cipro.gov.za/</t>
+    <t>https://www.cipc.co.za/</t>
   </si>
   <si>
     <t>ZA-CIT</t>
@@ -4366,7 +4390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E545"/>
+  <dimension ref="A1:E549"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5247,7 +5271,7 @@
         <v>8</v>
       </c>
       <c r="E52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -5907,7 +5931,7 @@
         <v>8</v>
       </c>
       <c r="E91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -7233,7 +7257,7 @@
         <v>8</v>
       </c>
       <c r="E169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -10732,7 +10756,7 @@
         <v>8</v>
       </c>
       <c r="E375" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -10961,10 +10985,10 @@
         <v>948</v>
       </c>
       <c r="B389" t="s">
+        <v>946</v>
+      </c>
+      <c r="C389" s="1" t="s">
         <v>949</v>
-      </c>
-      <c r="C389" s="1" t="s">
-        <v>950</v>
       </c>
       <c r="D389" t="s">
         <v>8</v>
@@ -10975,10 +10999,10 @@
     </row>
     <row r="390" spans="1:5">
       <c r="A390" t="s">
+        <v>950</v>
+      </c>
+      <c r="B390" t="s">
         <v>951</v>
-      </c>
-      <c r="B390" t="s">
-        <v>949</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>952</v>
@@ -10995,24 +11019,24 @@
         <v>953</v>
       </c>
       <c r="B391" t="s">
+        <v>951</v>
+      </c>
+      <c r="C391" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="C391" s="1" t="s">
-        <v>955</v>
-      </c>
       <c r="D391" t="s">
         <v>8</v>
       </c>
       <c r="E391" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392" spans="1:5">
       <c r="A392" t="s">
+        <v>955</v>
+      </c>
+      <c r="B392" t="s">
         <v>956</v>
-      </c>
-      <c r="B392" t="s">
-        <v>954</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>957</v>
@@ -11021,7 +11045,7 @@
         <v>8</v>
       </c>
       <c r="E392" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -11029,16 +11053,16 @@
         <v>958</v>
       </c>
       <c r="B393" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>959</v>
       </c>
       <c r="D393" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E393" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -11046,16 +11070,16 @@
         <v>960</v>
       </c>
       <c r="B394" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>961</v>
       </c>
       <c r="D394" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E394" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -11063,7 +11087,7 @@
         <v>962</v>
       </c>
       <c r="B395" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>963</v>
@@ -11072,7 +11096,7 @@
         <v>8</v>
       </c>
       <c r="E395" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -11080,10 +11104,10 @@
         <v>964</v>
       </c>
       <c r="B396" t="s">
+        <v>956</v>
+      </c>
+      <c r="C396" s="1" t="s">
         <v>965</v>
-      </c>
-      <c r="C396" s="1" t="s">
-        <v>966</v>
       </c>
       <c r="D396" t="s">
         <v>8</v>
@@ -11094,10 +11118,10 @@
     </row>
     <row r="397" spans="1:5">
       <c r="A397" t="s">
+        <v>966</v>
+      </c>
+      <c r="B397" t="s">
         <v>967</v>
-      </c>
-      <c r="B397" t="s">
-        <v>965</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>968</v>
@@ -11106,7 +11130,7 @@
         <v>8</v>
       </c>
       <c r="E397" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -11114,7 +11138,7 @@
         <v>969</v>
       </c>
       <c r="B398" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>970</v>
@@ -11131,7 +11155,7 @@
         <v>971</v>
       </c>
       <c r="B399" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>972</v>
@@ -11148,27 +11172,27 @@
         <v>973</v>
       </c>
       <c r="B400" t="s">
+        <v>967</v>
+      </c>
+      <c r="C400" s="1" t="s">
         <v>974</v>
       </c>
-      <c r="C400" s="1" t="s">
-        <v>975</v>
-      </c>
       <c r="D400" t="s">
         <v>8</v>
       </c>
       <c r="E400" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401" spans="1:5">
       <c r="A401" t="s">
+        <v>975</v>
+      </c>
+      <c r="B401" t="s">
         <v>976</v>
       </c>
-      <c r="B401" t="s">
+      <c r="C401" s="1" t="s">
         <v>977</v>
-      </c>
-      <c r="C401" s="1" t="s">
-        <v>978</v>
       </c>
       <c r="D401" t="s">
         <v>8</v>
@@ -11179,13 +11203,13 @@
     </row>
     <row r="402" spans="1:5">
       <c r="A402" t="s">
+        <v>978</v>
+      </c>
+      <c r="B402" t="s">
         <v>979</v>
       </c>
-      <c r="B402" t="s">
+      <c r="C402" s="1" t="s">
         <v>980</v>
-      </c>
-      <c r="C402" s="1" t="s">
-        <v>981</v>
       </c>
       <c r="D402" t="s">
         <v>8</v>
@@ -11196,13 +11220,13 @@
     </row>
     <row r="403" spans="1:5">
       <c r="A403" t="s">
+        <v>981</v>
+      </c>
+      <c r="B403" t="s">
         <v>982</v>
       </c>
-      <c r="B403" t="s">
+      <c r="C403" s="1" t="s">
         <v>983</v>
-      </c>
-      <c r="C403" s="1" t="s">
-        <v>984</v>
       </c>
       <c r="D403" t="s">
         <v>8</v>
@@ -11213,10 +11237,10 @@
     </row>
     <row r="404" spans="1:5">
       <c r="A404" t="s">
+        <v>984</v>
+      </c>
+      <c r="B404" t="s">
         <v>985</v>
-      </c>
-      <c r="B404" t="s">
-        <v>983</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>986</v>
@@ -11233,7 +11257,7 @@
         <v>987</v>
       </c>
       <c r="B405" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>988</v>
@@ -11250,10 +11274,10 @@
         <v>989</v>
       </c>
       <c r="B406" t="s">
+        <v>985</v>
+      </c>
+      <c r="C406" s="1" t="s">
         <v>990</v>
-      </c>
-      <c r="C406" s="1" t="s">
-        <v>991</v>
       </c>
       <c r="D406" t="s">
         <v>8</v>
@@ -11264,10 +11288,10 @@
     </row>
     <row r="407" spans="1:5">
       <c r="A407" t="s">
+        <v>991</v>
+      </c>
+      <c r="B407" t="s">
         <v>992</v>
-      </c>
-      <c r="B407" t="s">
-        <v>990</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>993</v>
@@ -11276,7 +11300,7 @@
         <v>8</v>
       </c>
       <c r="E407" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -11284,10 +11308,10 @@
         <v>994</v>
       </c>
       <c r="B408" t="s">
+        <v>992</v>
+      </c>
+      <c r="C408" s="1" t="s">
         <v>995</v>
-      </c>
-      <c r="C408" s="1" t="s">
-        <v>996</v>
       </c>
       <c r="D408" t="s">
         <v>8</v>
@@ -11298,27 +11322,27 @@
     </row>
     <row r="409" spans="1:5">
       <c r="A409" t="s">
+        <v>996</v>
+      </c>
+      <c r="B409" t="s">
         <v>997</v>
       </c>
-      <c r="B409" t="s">
+      <c r="C409" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="C409" s="1" t="s">
-        <v>999</v>
-      </c>
       <c r="D409" t="s">
         <v>8</v>
       </c>
       <c r="E409" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410" spans="1:5">
       <c r="A410" t="s">
+        <v>999</v>
+      </c>
+      <c r="B410" t="s">
         <v>1000</v>
-      </c>
-      <c r="B410" t="s">
-        <v>998</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>1001</v>
@@ -11327,7 +11351,7 @@
         <v>8</v>
       </c>
       <c r="E410" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -11335,7 +11359,7 @@
         <v>1002</v>
       </c>
       <c r="B411" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>1003</v>
@@ -11352,27 +11376,27 @@
         <v>1004</v>
       </c>
       <c r="B412" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C412" s="1" t="s">
         <v>1005</v>
       </c>
-      <c r="C412" s="1" t="s">
-        <v>1006</v>
-      </c>
       <c r="D412" t="s">
         <v>8</v>
       </c>
       <c r="E412" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413" spans="1:5">
       <c r="A413" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B413" t="s">
         <v>1007</v>
       </c>
-      <c r="B413" t="s">
+      <c r="C413" s="1" t="s">
         <v>1008</v>
-      </c>
-      <c r="C413" s="1" t="s">
-        <v>1009</v>
       </c>
       <c r="D413" t="s">
         <v>8</v>
@@ -11383,13 +11407,13 @@
     </row>
     <row r="414" spans="1:5">
       <c r="A414" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B414" t="s">
         <v>1010</v>
       </c>
-      <c r="B414" t="s">
+      <c r="C414" s="1" t="s">
         <v>1011</v>
-      </c>
-      <c r="C414" s="1" t="s">
-        <v>1012</v>
       </c>
       <c r="D414" t="s">
         <v>8</v>
@@ -11400,10 +11424,10 @@
     </row>
     <row r="415" spans="1:5">
       <c r="A415" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B415" t="s">
         <v>1013</v>
-      </c>
-      <c r="B415" t="s">
-        <v>1011</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>1014</v>
@@ -11412,7 +11436,7 @@
         <v>8</v>
       </c>
       <c r="E415" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -11420,24 +11444,24 @@
         <v>1015</v>
       </c>
       <c r="B416" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C416" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="C416" s="1" t="s">
-        <v>1017</v>
-      </c>
       <c r="D416" t="s">
         <v>8</v>
       </c>
       <c r="E416" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417" spans="1:5">
       <c r="A417" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B417" t="s">
         <v>1018</v>
-      </c>
-      <c r="B417" t="s">
-        <v>1016</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>1019</v>
@@ -11454,7 +11478,7 @@
         <v>1020</v>
       </c>
       <c r="B418" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>1021</v>
@@ -11463,7 +11487,7 @@
         <v>8</v>
       </c>
       <c r="E418" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -11471,24 +11495,24 @@
         <v>1022</v>
       </c>
       <c r="B419" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C419" s="1" t="s">
         <v>1023</v>
       </c>
-      <c r="C419" s="1" t="s">
-        <v>1024</v>
-      </c>
       <c r="D419" t="s">
         <v>8</v>
       </c>
       <c r="E419" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="420" spans="1:5">
       <c r="A420" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B420" t="s">
         <v>1025</v>
-      </c>
-      <c r="B420" t="s">
-        <v>1023</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>1026</v>
@@ -11497,7 +11521,7 @@
         <v>8</v>
       </c>
       <c r="E420" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -11505,7 +11529,7 @@
         <v>1027</v>
       </c>
       <c r="B421" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>1028</v>
@@ -11522,10 +11546,10 @@
         <v>1029</v>
       </c>
       <c r="B422" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C422" s="1" t="s">
         <v>1030</v>
-      </c>
-      <c r="C422" s="1" t="s">
-        <v>1031</v>
       </c>
       <c r="D422" t="s">
         <v>8</v>
@@ -11536,10 +11560,10 @@
     </row>
     <row r="423" spans="1:5">
       <c r="A423" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B423" t="s">
         <v>1032</v>
-      </c>
-      <c r="B423" t="s">
-        <v>1030</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>1033</v>
@@ -11548,7 +11572,7 @@
         <v>8</v>
       </c>
       <c r="E423" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -11556,7 +11580,7 @@
         <v>1034</v>
       </c>
       <c r="B424" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>1035</v>
@@ -11573,10 +11597,10 @@
         <v>1036</v>
       </c>
       <c r="B425" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C425" s="1" t="s">
         <v>1037</v>
-      </c>
-      <c r="C425" s="1" t="s">
-        <v>1038</v>
       </c>
       <c r="D425" t="s">
         <v>8</v>
@@ -11587,67 +11611,67 @@
     </row>
     <row r="426" spans="1:5">
       <c r="A426" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B426" t="s">
         <v>1039</v>
       </c>
-      <c r="B426" t="s">
+      <c r="C426" s="1" t="s">
         <v>1040</v>
       </c>
-      <c r="C426" s="1" t="s">
-        <v>1041</v>
-      </c>
       <c r="D426" t="s">
         <v>8</v>
       </c>
       <c r="E426" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="427" spans="1:5">
       <c r="A427" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B427" t="s">
         <v>1042</v>
       </c>
-      <c r="B427" t="s">
+      <c r="C427" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="C427" s="1" t="s">
-        <v>1044</v>
-      </c>
       <c r="D427" t="s">
         <v>8</v>
       </c>
       <c r="E427" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428" spans="1:5">
       <c r="A428" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B428" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C428" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="B428" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C428" s="1" t="s">
-        <v>1047</v>
-      </c>
       <c r="D428" t="s">
         <v>8</v>
       </c>
       <c r="E428" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429" spans="1:5">
       <c r="A429" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B429" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C429" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="B429" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C429" s="1" t="s">
-        <v>1050</v>
-      </c>
       <c r="D429" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E429" t="b">
         <v>0</v>
@@ -11655,13 +11679,13 @@
     </row>
     <row r="430" spans="1:5">
       <c r="A430" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B430" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C430" s="1" t="s">
         <v>1051</v>
-      </c>
-      <c r="B430" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C430" s="1" t="s">
-        <v>1052</v>
       </c>
       <c r="D430" t="s">
         <v>8</v>
@@ -11672,10 +11696,10 @@
     </row>
     <row r="431" spans="1:5">
       <c r="A431" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B431" t="s">
         <v>1053</v>
-      </c>
-      <c r="B431" t="s">
-        <v>1049</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>1054</v>
@@ -11692,7 +11716,7 @@
         <v>1055</v>
       </c>
       <c r="B432" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>1056</v>
@@ -11701,7 +11725,7 @@
         <v>8</v>
       </c>
       <c r="E432" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -11709,13 +11733,13 @@
         <v>1057</v>
       </c>
       <c r="B433" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C433" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="C433" s="1" t="s">
-        <v>1059</v>
-      </c>
       <c r="D433" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E433" t="b">
         <v>0</v>
@@ -11723,27 +11747,27 @@
     </row>
     <row r="434" spans="1:5">
       <c r="A434" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B434" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C434" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="B434" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C434" s="1" t="s">
-        <v>1061</v>
-      </c>
       <c r="D434" t="s">
         <v>8</v>
       </c>
       <c r="E434" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435" spans="1:5">
       <c r="A435" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B435" t="s">
         <v>1062</v>
-      </c>
-      <c r="B435" t="s">
-        <v>1058</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>1063</v>
@@ -11752,7 +11776,7 @@
         <v>8</v>
       </c>
       <c r="E435" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -11760,10 +11784,10 @@
         <v>1064</v>
       </c>
       <c r="B436" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C436" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="C436" s="1" t="s">
-        <v>1066</v>
       </c>
       <c r="D436" t="s">
         <v>8</v>
@@ -11774,44 +11798,44 @@
     </row>
     <row r="437" spans="1:5">
       <c r="A437" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B437" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C437" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="B437" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C437" s="1" t="s">
-        <v>1069</v>
-      </c>
       <c r="D437" t="s">
         <v>8</v>
       </c>
       <c r="E437" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438" spans="1:5">
       <c r="A438" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B438" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C438" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="B438" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C438" s="1" t="s">
-        <v>1071</v>
-      </c>
       <c r="D438" t="s">
         <v>8</v>
       </c>
       <c r="E438" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="439" spans="1:5">
       <c r="A439" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B439" t="s">
         <v>1072</v>
-      </c>
-      <c r="B439" t="s">
-        <v>1068</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>1073</v>
@@ -11820,7 +11844,7 @@
         <v>8</v>
       </c>
       <c r="E439" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -11828,58 +11852,58 @@
         <v>1074</v>
       </c>
       <c r="B440" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C440" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="C440" s="1" t="s">
-        <v>1076</v>
-      </c>
       <c r="D440" t="s">
         <v>8</v>
       </c>
       <c r="E440" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441" spans="1:5">
       <c r="A441" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B441" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C441" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="B441" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C441" s="1" t="s">
-        <v>1079</v>
-      </c>
       <c r="D441" t="s">
         <v>8</v>
       </c>
       <c r="E441" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442" spans="1:5">
       <c r="A442" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B442" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C442" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="B442" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C442" s="1" t="s">
-        <v>1081</v>
-      </c>
       <c r="D442" t="s">
         <v>8</v>
       </c>
       <c r="E442" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443" spans="1:5">
       <c r="A443" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B443" t="s">
         <v>1082</v>
-      </c>
-      <c r="B443" t="s">
-        <v>1078</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>1083</v>
@@ -11896,24 +11920,24 @@
         <v>1084</v>
       </c>
       <c r="B444" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="D444" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E444" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445" spans="1:5">
       <c r="A445" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B445" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>1087</v>
@@ -11922,7 +11946,7 @@
         <v>8</v>
       </c>
       <c r="E445" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -11930,13 +11954,13 @@
         <v>1088</v>
       </c>
       <c r="B446" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="D446" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E446" t="b">
         <v>0</v>
@@ -11944,10 +11968,10 @@
     </row>
     <row r="447" spans="1:5">
       <c r="A447" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B447" t="s">
         <v>1090</v>
-      </c>
-      <c r="B447" t="s">
-        <v>1086</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>1091</v>
@@ -11956,7 +11980,7 @@
         <v>8</v>
       </c>
       <c r="E447" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -11964,10 +11988,10 @@
         <v>1092</v>
       </c>
       <c r="B448" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C448" s="1" t="s">
         <v>1093</v>
-      </c>
-      <c r="C448" s="1" t="s">
-        <v>1094</v>
       </c>
       <c r="D448" t="s">
         <v>8</v>
@@ -11978,47 +12002,47 @@
     </row>
     <row r="449" spans="1:5">
       <c r="A449" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B449" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C449" s="1" t="s">
         <v>1095</v>
       </c>
-      <c r="B449" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C449" s="1" t="s">
-        <v>1097</v>
-      </c>
       <c r="D449" t="s">
         <v>8</v>
       </c>
       <c r="E449" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="450" spans="1:5">
       <c r="A450" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B450" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C450" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="B450" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C450" s="1" t="s">
-        <v>1099</v>
-      </c>
       <c r="D450" t="s">
         <v>8</v>
       </c>
       <c r="E450" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451" spans="1:5">
       <c r="A451" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B451" t="s">
         <v>1100</v>
       </c>
-      <c r="B451" t="s">
+      <c r="C451" s="1" t="s">
         <v>1101</v>
-      </c>
-      <c r="C451" s="1" t="s">
-        <v>1102</v>
       </c>
       <c r="D451" t="s">
         <v>8</v>
@@ -12029,47 +12053,47 @@
     </row>
     <row r="452" spans="1:5">
       <c r="A452" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B452" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C452" s="1" t="s">
         <v>1103</v>
       </c>
-      <c r="B452" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C452" s="1" t="s">
-        <v>1104</v>
-      </c>
       <c r="D452" t="s">
         <v>8</v>
       </c>
       <c r="E452" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453" spans="1:5">
       <c r="A453" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B453" t="s">
         <v>1105</v>
       </c>
-      <c r="B453" t="s">
+      <c r="C453" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="C453" s="1" t="s">
-        <v>1107</v>
-      </c>
       <c r="D453" t="s">
         <v>8</v>
       </c>
       <c r="E453" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454" spans="1:5">
       <c r="A454" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B454" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C454" s="1" t="s">
         <v>1108</v>
-      </c>
-      <c r="B454" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C454" s="1" t="s">
-        <v>1110</v>
       </c>
       <c r="D454" t="s">
         <v>8</v>
@@ -12080,10 +12104,13 @@
     </row>
     <row r="455" spans="1:5">
       <c r="A455" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B455" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C455" s="1" t="s">
         <v>1111</v>
-      </c>
-      <c r="B455" t="s">
-        <v>1109</v>
       </c>
       <c r="D455" t="s">
         <v>8</v>
@@ -12114,10 +12141,7 @@
         <v>1115</v>
       </c>
       <c r="B457" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C457" s="1" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="D457" t="s">
         <v>8</v>
@@ -12128,13 +12152,13 @@
     </row>
     <row r="458" spans="1:5">
       <c r="A458" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C458" s="1" t="s">
         <v>1118</v>
-      </c>
-      <c r="B458" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C458" s="1" t="s">
-        <v>1119</v>
       </c>
       <c r="D458" t="s">
         <v>8</v>
@@ -12145,13 +12169,13 @@
     </row>
     <row r="459" spans="1:5">
       <c r="A459" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B459" t="s">
         <v>1120</v>
       </c>
-      <c r="B459" t="s">
+      <c r="C459" s="1" t="s">
         <v>1121</v>
-      </c>
-      <c r="C459" s="1" t="s">
-        <v>1122</v>
       </c>
       <c r="D459" t="s">
         <v>8</v>
@@ -12162,13 +12186,13 @@
     </row>
     <row r="460" spans="1:5">
       <c r="A460" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C460" s="1" t="s">
         <v>1123</v>
-      </c>
-      <c r="B460" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C460" s="1" t="s">
-        <v>1125</v>
       </c>
       <c r="D460" t="s">
         <v>8</v>
@@ -12179,64 +12203,64 @@
     </row>
     <row r="461" spans="1:5">
       <c r="A461" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C461" s="1" t="s">
         <v>1126</v>
       </c>
-      <c r="B461" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C461" s="1" t="s">
-        <v>1128</v>
-      </c>
       <c r="D461" t="s">
         <v>8</v>
       </c>
       <c r="E461" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="462" spans="1:5">
       <c r="A462" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C462" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="B462" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C462" s="1" t="s">
-        <v>1130</v>
-      </c>
       <c r="D462" t="s">
         <v>8</v>
       </c>
       <c r="E462" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="463" spans="1:5">
       <c r="A463" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B463" t="s">
         <v>1131</v>
       </c>
-      <c r="B463" t="s">
+      <c r="C463" s="1" t="s">
         <v>1132</v>
       </c>
-      <c r="C463" s="1" t="s">
-        <v>1133</v>
-      </c>
       <c r="D463" t="s">
         <v>8</v>
       </c>
       <c r="E463" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464" spans="1:5">
       <c r="A464" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C464" s="1" t="s">
         <v>1134</v>
-      </c>
-      <c r="B464" t="s">
-        <v>1135</v>
-      </c>
-      <c r="C464" s="1" t="s">
-        <v>1136</v>
       </c>
       <c r="D464" t="s">
         <v>8</v>
@@ -12247,13 +12271,13 @@
     </row>
     <row r="465" spans="1:5">
       <c r="A465" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C465" s="1" t="s">
         <v>1137</v>
-      </c>
-      <c r="B465" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C465" s="1" t="s">
-        <v>1139</v>
       </c>
       <c r="D465" t="s">
         <v>8</v>
@@ -12264,13 +12288,13 @@
     </row>
     <row r="466" spans="1:5">
       <c r="A466" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C466" s="1" t="s">
         <v>1140</v>
-      </c>
-      <c r="B466" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C466" s="1" t="s">
-        <v>1142</v>
       </c>
       <c r="D466" t="s">
         <v>8</v>
@@ -12281,13 +12305,13 @@
     </row>
     <row r="467" spans="1:5">
       <c r="A467" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C467" s="1" t="s">
         <v>1143</v>
-      </c>
-      <c r="B467" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C467" s="1" t="s">
-        <v>1145</v>
       </c>
       <c r="D467" t="s">
         <v>8</v>
@@ -12298,27 +12322,27 @@
     </row>
     <row r="468" spans="1:5">
       <c r="A468" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C468" s="1" t="s">
         <v>1146</v>
       </c>
-      <c r="B468" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C468" s="1" t="s">
-        <v>1147</v>
-      </c>
       <c r="D468" t="s">
         <v>8</v>
       </c>
       <c r="E468" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469" spans="1:5">
       <c r="A469" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B469" t="s">
         <v>1148</v>
-      </c>
-      <c r="B469" t="s">
-        <v>1144</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>1149</v>
@@ -12335,10 +12359,10 @@
         <v>1150</v>
       </c>
       <c r="B470" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C470" s="1" t="s">
         <v>1151</v>
-      </c>
-      <c r="C470" s="1" t="s">
-        <v>1152</v>
       </c>
       <c r="D470" t="s">
         <v>8</v>
@@ -12349,13 +12373,13 @@
     </row>
     <row r="471" spans="1:5">
       <c r="A471" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C471" s="1" t="s">
         <v>1153</v>
-      </c>
-      <c r="B471" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C471" s="1" t="s">
-        <v>1155</v>
       </c>
       <c r="D471" t="s">
         <v>8</v>
@@ -12366,30 +12390,30 @@
     </row>
     <row r="472" spans="1:5">
       <c r="A472" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C472" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="B472" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C472" s="1" t="s">
-        <v>1158</v>
-      </c>
       <c r="D472" t="s">
         <v>8</v>
       </c>
       <c r="E472" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473" spans="1:5">
       <c r="A473" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C473" s="1" t="s">
         <v>1159</v>
-      </c>
-      <c r="B473" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C473" s="1" t="s">
-        <v>1161</v>
       </c>
       <c r="D473" t="s">
         <v>8</v>
@@ -12400,30 +12424,30 @@
     </row>
     <row r="474" spans="1:5">
       <c r="A474" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C474" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="B474" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C474" s="1" t="s">
-        <v>1164</v>
-      </c>
       <c r="D474" t="s">
         <v>8</v>
       </c>
       <c r="E474" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475" spans="1:5">
       <c r="A475" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C475" s="1" t="s">
         <v>1165</v>
-      </c>
-      <c r="B475" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C475" s="1" t="s">
-        <v>1166</v>
       </c>
       <c r="D475" t="s">
         <v>8</v>
@@ -12434,13 +12458,13 @@
     </row>
     <row r="476" spans="1:5">
       <c r="A476" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B476" t="s">
         <v>1167</v>
       </c>
-      <c r="B476" t="s">
+      <c r="C476" s="1" t="s">
         <v>1168</v>
-      </c>
-      <c r="C476" s="1" t="s">
-        <v>1169</v>
       </c>
       <c r="D476" t="s">
         <v>8</v>
@@ -12451,13 +12475,13 @@
     </row>
     <row r="477" spans="1:5">
       <c r="A477" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C477" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="B477" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C477" s="1" t="s">
-        <v>1172</v>
       </c>
       <c r="D477" t="s">
         <v>8</v>
@@ -12468,27 +12492,27 @@
     </row>
     <row r="478" spans="1:5">
       <c r="A478" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C478" s="1" t="s">
         <v>1173</v>
       </c>
-      <c r="B478" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C478" s="1" t="s">
-        <v>1174</v>
-      </c>
       <c r="D478" t="s">
         <v>8</v>
       </c>
       <c r="E478" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="479" spans="1:5">
       <c r="A479" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B479" t="s">
         <v>1175</v>
-      </c>
-      <c r="B479" t="s">
-        <v>1171</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>1176</v>
@@ -12505,27 +12529,27 @@
         <v>1177</v>
       </c>
       <c r="B480" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C480" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="C480" s="1" t="s">
-        <v>1179</v>
-      </c>
       <c r="D480" t="s">
         <v>8</v>
       </c>
       <c r="E480" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481" spans="1:5">
       <c r="A481" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C481" s="1" t="s">
         <v>1180</v>
-      </c>
-      <c r="B481" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C481" s="1" t="s">
-        <v>1182</v>
       </c>
       <c r="D481" t="s">
         <v>8</v>
@@ -12536,13 +12560,13 @@
     </row>
     <row r="482" spans="1:5">
       <c r="A482" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="B482" t="s">
-        <v>1184</v>
+        <v>1175</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="D482" t="s">
         <v>8</v>
@@ -12553,13 +12577,13 @@
     </row>
     <row r="483" spans="1:5">
       <c r="A483" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="B483" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="D483" t="s">
         <v>8</v>
@@ -12570,30 +12594,30 @@
     </row>
     <row r="484" spans="1:5">
       <c r="A484" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="B484" t="s">
         <v>1187</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="D484" t="s">
         <v>8</v>
       </c>
       <c r="E484" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="485" spans="1:5">
       <c r="A485" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C485" s="1" t="s">
         <v>1191</v>
-      </c>
-      <c r="B485" t="s">
-        <v>1187</v>
-      </c>
-      <c r="C485" s="1" t="s">
-        <v>1192</v>
       </c>
       <c r="D485" t="s">
         <v>8</v>
@@ -12604,10 +12628,10 @@
     </row>
     <row r="486" spans="1:5">
       <c r="A486" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B486" t="s">
         <v>1193</v>
-      </c>
-      <c r="B486" t="s">
-        <v>1187</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>1194</v>
@@ -12624,27 +12648,27 @@
         <v>1195</v>
       </c>
       <c r="B487" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C487" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="C487" s="1" t="s">
-        <v>1197</v>
-      </c>
       <c r="D487" t="s">
         <v>8</v>
       </c>
       <c r="E487" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488" spans="1:5">
       <c r="A488" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C488" s="1" t="s">
         <v>1198</v>
-      </c>
-      <c r="B488" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C488" s="1" t="s">
-        <v>1199</v>
       </c>
       <c r="D488" t="s">
         <v>8</v>
@@ -12655,13 +12679,13 @@
     </row>
     <row r="489" spans="1:5">
       <c r="A489" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C489" s="1" t="s">
         <v>1200</v>
-      </c>
-      <c r="B489" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C489" s="1" t="s">
-        <v>1202</v>
       </c>
       <c r="D489" t="s">
         <v>8</v>
@@ -12672,33 +12696,33 @@
     </row>
     <row r="490" spans="1:5">
       <c r="A490" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C490" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="B490" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C490" s="1" t="s">
-        <v>1204</v>
-      </c>
       <c r="D490" t="s">
         <v>8</v>
       </c>
       <c r="E490" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="491" spans="1:5">
       <c r="A491" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C491" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="B491" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C491" s="1" t="s">
-        <v>1206</v>
-      </c>
       <c r="D491" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E491" t="b">
         <v>0</v>
@@ -12706,10 +12730,10 @@
     </row>
     <row r="492" spans="1:5">
       <c r="A492" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B492" t="s">
         <v>1207</v>
-      </c>
-      <c r="B492" t="s">
-        <v>1201</v>
       </c>
       <c r="C492" s="1" t="s">
         <v>1208</v>
@@ -12718,7 +12742,7 @@
         <v>8</v>
       </c>
       <c r="E492" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -12726,7 +12750,7 @@
         <v>1209</v>
       </c>
       <c r="B493" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="C493" s="1" t="s">
         <v>1210</v>
@@ -12735,7 +12759,7 @@
         <v>8</v>
       </c>
       <c r="E493" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -12743,13 +12767,13 @@
         <v>1211</v>
       </c>
       <c r="B494" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C494" s="1" t="s">
         <v>1212</v>
       </c>
-      <c r="C494" s="1" t="s">
-        <v>1213</v>
-      </c>
       <c r="D494" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E494" t="b">
         <v>0</v>
@@ -12757,47 +12781,47 @@
     </row>
     <row r="495" spans="1:5">
       <c r="A495" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C495" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="B495" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C495" s="1" t="s">
-        <v>1216</v>
-      </c>
       <c r="D495" t="s">
         <v>8</v>
       </c>
       <c r="E495" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496" spans="1:5">
       <c r="A496" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B496" t="s">
-        <v>1215</v>
+        <v>1207</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="D496" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E496" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="497" spans="1:5">
       <c r="A497" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C497" s="1" t="s">
         <v>1219</v>
-      </c>
-      <c r="B497" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C497" s="1" t="s">
-        <v>1220</v>
       </c>
       <c r="D497" t="s">
         <v>8</v>
@@ -12808,10 +12832,10 @@
     </row>
     <row r="498" spans="1:5">
       <c r="A498" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B498" t="s">
         <v>1221</v>
-      </c>
-      <c r="B498" t="s">
-        <v>1215</v>
       </c>
       <c r="C498" s="1" t="s">
         <v>1222</v>
@@ -12820,7 +12844,7 @@
         <v>8</v>
       </c>
       <c r="E498" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -12828,13 +12852,13 @@
         <v>1223</v>
       </c>
       <c r="B499" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="C499" s="1" t="s">
         <v>1224</v>
       </c>
       <c r="D499" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E499" t="b">
         <v>0</v>
@@ -12845,10 +12869,10 @@
         <v>1225</v>
       </c>
       <c r="B500" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C500" s="1" t="s">
         <v>1226</v>
-      </c>
-      <c r="C500" s="1" t="s">
-        <v>1227</v>
       </c>
       <c r="D500" t="s">
         <v>8</v>
@@ -12859,30 +12883,30 @@
     </row>
     <row r="501" spans="1:5">
       <c r="A501" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C501" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="B501" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C501" s="1" t="s">
-        <v>1230</v>
-      </c>
       <c r="D501" t="s">
         <v>8</v>
       </c>
       <c r="E501" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502" spans="1:5">
       <c r="A502" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B502" t="s">
-        <v>1229</v>
+        <v>1221</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="D502" t="s">
         <v>8</v>
@@ -12893,13 +12917,13 @@
     </row>
     <row r="503" spans="1:5">
       <c r="A503" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C503" s="1" t="s">
         <v>1233</v>
-      </c>
-      <c r="B503" t="s">
-        <v>1234</v>
-      </c>
-      <c r="C503" s="1" t="s">
-        <v>1235</v>
       </c>
       <c r="D503" t="s">
         <v>8</v>
@@ -12910,13 +12934,13 @@
     </row>
     <row r="504" spans="1:5">
       <c r="A504" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C504" s="1" t="s">
         <v>1236</v>
-      </c>
-      <c r="B504" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C504" s="1" t="s">
-        <v>1238</v>
       </c>
       <c r="D504" t="s">
         <v>8</v>
@@ -12927,13 +12951,13 @@
     </row>
     <row r="505" spans="1:5">
       <c r="A505" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B505" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="D505" t="s">
         <v>8</v>
@@ -12944,13 +12968,13 @@
     </row>
     <row r="506" spans="1:5">
       <c r="A506" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="B506" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="D506" t="s">
         <v>8</v>
@@ -12961,13 +12985,13 @@
     </row>
     <row r="507" spans="1:5">
       <c r="A507" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="B507" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="D507" t="s">
         <v>8</v>
@@ -12978,13 +13002,13 @@
     </row>
     <row r="508" spans="1:5">
       <c r="A508" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="B508" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="D508" t="s">
         <v>8</v>
@@ -12995,13 +13019,13 @@
     </row>
     <row r="509" spans="1:5">
       <c r="A509" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="B509" t="s">
         <v>1249</v>
       </c>
       <c r="C509" s="1" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D509" t="s">
         <v>8</v>
@@ -13012,13 +13036,13 @@
     </row>
     <row r="510" spans="1:5">
       <c r="A510" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C510" s="1" t="s">
         <v>1253</v>
-      </c>
-      <c r="B510" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C510" s="1" t="s">
-        <v>1255</v>
       </c>
       <c r="D510" t="s">
         <v>8</v>
@@ -13029,13 +13053,13 @@
     </row>
     <row r="511" spans="1:5">
       <c r="A511" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C511" s="1" t="s">
         <v>1256</v>
-      </c>
-      <c r="B511" t="s">
-        <v>1257</v>
-      </c>
-      <c r="C511" s="1" t="s">
-        <v>1258</v>
       </c>
       <c r="D511" t="s">
         <v>8</v>
@@ -13046,13 +13070,13 @@
     </row>
     <row r="512" spans="1:5">
       <c r="A512" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="B512" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="D512" t="s">
         <v>8</v>
@@ -13063,7 +13087,13 @@
     </row>
     <row r="513" spans="1:5">
       <c r="A513" t="s">
-        <v>1262</v>
+        <v>1259</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C513" s="1" t="s">
+        <v>1260</v>
       </c>
       <c r="D513" t="s">
         <v>8</v>
@@ -13074,41 +13104,44 @@
     </row>
     <row r="514" spans="1:5">
       <c r="A514" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C514" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="C514" s="1" t="s">
-        <v>1264</v>
-      </c>
       <c r="D514" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E514" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="515" spans="1:5">
       <c r="A515" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B515" t="s">
         <v>1265</v>
       </c>
-      <c r="B515" t="s">
+      <c r="C515" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="C515" s="1" t="s">
-        <v>1267</v>
-      </c>
       <c r="D515" t="s">
         <v>8</v>
       </c>
       <c r="E515" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="516" spans="1:5">
       <c r="A516" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B516" t="s">
         <v>1268</v>
-      </c>
-      <c r="B516" t="s">
-        <v>1266</v>
       </c>
       <c r="C516" s="1" t="s">
         <v>1269</v>
@@ -13124,9 +13157,6 @@
       <c r="A517" t="s">
         <v>1270</v>
       </c>
-      <c r="C517" s="1" t="s">
-        <v>1271</v>
-      </c>
       <c r="D517" t="s">
         <v>8</v>
       </c>
@@ -13136,24 +13166,24 @@
     </row>
     <row r="518" spans="1:5">
       <c r="A518" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C518" s="1" t="s">
         <v>1272</v>
       </c>
-      <c r="C518" s="1" t="s">
-        <v>1273</v>
-      </c>
       <c r="D518" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E518" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519" spans="1:5">
       <c r="A519" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B519" t="s">
         <v>1274</v>
-      </c>
-      <c r="B519" t="s">
-        <v>1266</v>
       </c>
       <c r="C519" s="1" t="s">
         <v>1275</v>
@@ -13170,10 +13200,10 @@
         <v>1276</v>
       </c>
       <c r="B520" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C520" s="1" t="s">
         <v>1277</v>
-      </c>
-      <c r="C520" s="1" t="s">
-        <v>1278</v>
       </c>
       <c r="D520" t="s">
         <v>8</v>
@@ -13184,47 +13214,44 @@
     </row>
     <row r="521" spans="1:5">
       <c r="A521" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C521" s="1" t="s">
         <v>1279</v>
       </c>
-      <c r="B521" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C521" s="1" t="s">
-        <v>1280</v>
-      </c>
       <c r="D521" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E521" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522" spans="1:5">
       <c r="A522" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C522" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="B522" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C522" s="1" t="s">
-        <v>1282</v>
-      </c>
       <c r="D522" t="s">
         <v>8</v>
       </c>
       <c r="E522" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="523" spans="1:5">
       <c r="A523" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C523" s="1" t="s">
         <v>1283</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C523" s="1" t="s">
-        <v>1284</v>
       </c>
       <c r="D523" t="s">
         <v>8</v>
@@ -13235,13 +13262,13 @@
     </row>
     <row r="524" spans="1:5">
       <c r="A524" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B524" t="s">
         <v>1285</v>
       </c>
-      <c r="B524" t="s">
+      <c r="C524" s="1" t="s">
         <v>1286</v>
-      </c>
-      <c r="C524" s="1" t="s">
-        <v>1287</v>
       </c>
       <c r="D524" t="s">
         <v>8</v>
@@ -13252,24 +13279,30 @@
     </row>
     <row r="525" spans="1:5">
       <c r="A525" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C525" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="C525" s="1" t="s">
-        <v>1289</v>
-      </c>
       <c r="D525" t="s">
         <v>8</v>
       </c>
       <c r="E525" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="526" spans="1:5">
       <c r="A526" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C526" s="1" t="s">
         <v>1290</v>
-      </c>
-      <c r="C526" s="1" t="s">
-        <v>1291</v>
       </c>
       <c r="D526" t="s">
         <v>8</v>
@@ -13280,13 +13313,13 @@
     </row>
     <row r="527" spans="1:5">
       <c r="A527" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C527" s="1" t="s">
         <v>1292</v>
-      </c>
-      <c r="B527" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C527" s="1" t="s">
-        <v>1293</v>
       </c>
       <c r="D527" t="s">
         <v>8</v>
@@ -13297,13 +13330,13 @@
     </row>
     <row r="528" spans="1:5">
       <c r="A528" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B528" t="s">
         <v>1294</v>
       </c>
-      <c r="B528" t="s">
+      <c r="C528" s="1" t="s">
         <v>1295</v>
-      </c>
-      <c r="C528" s="1" t="s">
-        <v>1296</v>
       </c>
       <c r="D528" t="s">
         <v>8</v>
@@ -13314,30 +13347,24 @@
     </row>
     <row r="529" spans="1:5">
       <c r="A529" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C529" s="1" t="s">
         <v>1297</v>
       </c>
-      <c r="B529" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C529" s="1" t="s">
-        <v>1299</v>
-      </c>
       <c r="D529" t="s">
         <v>8</v>
       </c>
       <c r="E529" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="530" spans="1:5">
       <c r="A530" t="s">
-        <v>1300</v>
-      </c>
-      <c r="B530" t="s">
         <v>1298</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D530" t="s">
         <v>8</v>
@@ -13348,30 +13375,30 @@
     </row>
     <row r="531" spans="1:5">
       <c r="A531" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B531" t="s">
-        <v>1298</v>
+        <v>1274</v>
       </c>
       <c r="C531" s="1" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="D531" t="s">
         <v>8</v>
       </c>
       <c r="E531" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="532" spans="1:5">
       <c r="A532" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C532" s="1" t="s">
         <v>1304</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C532" s="1" t="s">
-        <v>1305</v>
       </c>
       <c r="D532" t="s">
         <v>8</v>
@@ -13382,13 +13409,13 @@
     </row>
     <row r="533" spans="1:5">
       <c r="A533" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B533" t="s">
         <v>1306</v>
       </c>
-      <c r="B533" t="s">
+      <c r="C533" s="1" t="s">
         <v>1307</v>
-      </c>
-      <c r="C533" s="1" t="s">
-        <v>1308</v>
       </c>
       <c r="D533" t="s">
         <v>8</v>
@@ -13399,30 +13426,30 @@
     </row>
     <row r="534" spans="1:5">
       <c r="A534" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C534" s="1" t="s">
         <v>1309</v>
       </c>
-      <c r="B534" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C534" s="1" t="s">
-        <v>1311</v>
-      </c>
       <c r="D534" t="s">
         <v>8</v>
       </c>
       <c r="E534" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="535" spans="1:5">
       <c r="A535" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="B535" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="C535" s="1" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="D535" t="s">
         <v>8</v>
@@ -13433,30 +13460,30 @@
     </row>
     <row r="536" spans="1:5">
       <c r="A536" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="B536" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="C536" s="1" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D536" t="s">
         <v>8</v>
       </c>
       <c r="E536" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:5">
       <c r="A537" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C537" s="1" t="s">
         <v>1316</v>
-      </c>
-      <c r="B537" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C537" s="1" t="s">
-        <v>1317</v>
       </c>
       <c r="D537" t="s">
         <v>8</v>
@@ -13467,16 +13494,16 @@
     </row>
     <row r="538" spans="1:5">
       <c r="A538" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B538" t="s">
         <v>1318</v>
-      </c>
-      <c r="B538" t="s">
-        <v>1310</v>
       </c>
       <c r="C538" s="1" t="s">
         <v>1319</v>
       </c>
       <c r="D538" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E538" t="b">
         <v>0</v>
@@ -13487,44 +13514,44 @@
         <v>1320</v>
       </c>
       <c r="B539" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C539" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="C539" s="1" t="s">
-        <v>1322</v>
-      </c>
       <c r="D539" t="s">
         <v>8</v>
       </c>
       <c r="E539" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540" spans="1:5">
       <c r="A540" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C540" s="1" t="s">
         <v>1323</v>
       </c>
-      <c r="B540" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C540" s="1" t="s">
-        <v>1324</v>
-      </c>
       <c r="D540" t="s">
         <v>8</v>
       </c>
       <c r="E540" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541" spans="1:5">
       <c r="A541" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C541" s="1" t="s">
         <v>1325</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C541" s="1" t="s">
-        <v>1326</v>
       </c>
       <c r="D541" t="s">
         <v>8</v>
@@ -13535,33 +13562,36 @@
     </row>
     <row r="542" spans="1:5">
       <c r="A542" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C542" s="1" t="s">
         <v>1327</v>
       </c>
-      <c r="B542" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C542" s="1" t="s">
-        <v>1329</v>
-      </c>
       <c r="D542" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E542" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="543" spans="1:5">
       <c r="A543" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C543" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="B543" t="s">
-        <v>1328</v>
-      </c>
       <c r="D543" t="s">
         <v>8</v>
       </c>
       <c r="E543" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="544" spans="1:5">
@@ -13569,7 +13599,7 @@
         <v>1331</v>
       </c>
       <c r="B544" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C544" s="1" t="s">
         <v>1332</v>
@@ -13586,15 +13616,80 @@
         <v>1333</v>
       </c>
       <c r="B545" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C545" s="1" t="s">
         <v>1334</v>
       </c>
-      <c r="C545" s="1" t="s">
+      <c r="D545" t="s">
+        <v>8</v>
+      </c>
+      <c r="E545" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5">
+      <c r="A546" t="s">
         <v>1335</v>
       </c>
-      <c r="D545" t="s">
-        <v>8</v>
-      </c>
-      <c r="E545" t="b">
+      <c r="B546" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C546" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D546" t="s">
+        <v>8</v>
+      </c>
+      <c r="E546" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5">
+      <c r="A547" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D547" t="s">
+        <v>8</v>
+      </c>
+      <c r="E547" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5">
+      <c r="A548" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C548" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D548" t="s">
+        <v>8</v>
+      </c>
+      <c r="E548" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5">
+      <c r="A549" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C549" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D549" t="s">
+        <v>8</v>
+      </c>
+      <c r="E549" t="b">
         <v>1</v>
       </c>
     </row>
@@ -14050,8 +14145,8 @@
     <hyperlink ref="C452" r:id="rId448"/>
     <hyperlink ref="C453" r:id="rId449"/>
     <hyperlink ref="C454" r:id="rId450"/>
-    <hyperlink ref="C456" r:id="rId451"/>
-    <hyperlink ref="C457" r:id="rId452"/>
+    <hyperlink ref="C455" r:id="rId451"/>
+    <hyperlink ref="C456" r:id="rId452"/>
     <hyperlink ref="C458" r:id="rId453"/>
     <hyperlink ref="C459" r:id="rId454"/>
     <hyperlink ref="C460" r:id="rId455"/>
@@ -14069,9 +14164,9 @@
     <hyperlink ref="C472" r:id="rId467"/>
     <hyperlink ref="C473" r:id="rId468"/>
     <hyperlink ref="C474" r:id="rId469"/>
-    <hyperlink ref="C475" r:id="rId470" location="/recherche-pm"/>
+    <hyperlink ref="C475" r:id="rId470"/>
     <hyperlink ref="C476" r:id="rId471"/>
-    <hyperlink ref="C477" r:id="rId472"/>
+    <hyperlink ref="C477" r:id="rId472" location="/recherche-pm"/>
     <hyperlink ref="C478" r:id="rId473"/>
     <hyperlink ref="C479" r:id="rId474"/>
     <hyperlink ref="C480" r:id="rId475"/>
@@ -14107,10 +14202,10 @@
     <hyperlink ref="C510" r:id="rId505"/>
     <hyperlink ref="C511" r:id="rId506"/>
     <hyperlink ref="C512" r:id="rId507"/>
-    <hyperlink ref="C514" r:id="rId508"/>
-    <hyperlink ref="C515" r:id="rId509"/>
-    <hyperlink ref="C516" r:id="rId510"/>
-    <hyperlink ref="C517" r:id="rId511"/>
+    <hyperlink ref="C513" r:id="rId508"/>
+    <hyperlink ref="C514" r:id="rId509"/>
+    <hyperlink ref="C515" r:id="rId510"/>
+    <hyperlink ref="C516" r:id="rId511"/>
     <hyperlink ref="C518" r:id="rId512"/>
     <hyperlink ref="C519" r:id="rId513"/>
     <hyperlink ref="C520" r:id="rId514"/>
@@ -14136,8 +14231,12 @@
     <hyperlink ref="C540" r:id="rId534"/>
     <hyperlink ref="C541" r:id="rId535"/>
     <hyperlink ref="C542" r:id="rId536"/>
-    <hyperlink ref="C544" r:id="rId537"/>
-    <hyperlink ref="C545" r:id="rId538"/>
+    <hyperlink ref="C543" r:id="rId537"/>
+    <hyperlink ref="C544" r:id="rId538"/>
+    <hyperlink ref="C545" r:id="rId539"/>
+    <hyperlink ref="C546" r:id="rId540"/>
+    <hyperlink ref="C548" r:id="rId541"/>
+    <hyperlink ref="C549" r:id="rId542"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
